--- a/src/test/resources/TestData.xlsx
+++ b/src/test/resources/TestData.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="7">
   <si>
     <t>username</t>
   </si>
@@ -32,18 +32,6 @@
   </si>
   <si>
     <t>admin@124</t>
-  </si>
-  <si>
-    <t>admin2@gmail.com</t>
-  </si>
-  <si>
-    <t>admin@125</t>
-  </si>
-  <si>
-    <t>admin3@gmail.com</t>
-  </si>
-  <si>
-    <t>admin@126</t>
   </si>
 </sst>
 </file>
@@ -332,22 +320,6 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
